--- a/src/scripts/Model_Stats.xlsx
+++ b/src/scripts/Model_Stats.xlsx
@@ -2479,14 +2479,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MobileNet V2 (TF_ver_2.0)</t>
+          <t>MobileNet V3</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>69.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="D4" t="n">
         <v>94.7</v>
@@ -2495,7 +2495,7 @@
         <v>11.45479578442652</v>
       </c>
       <c r="F4" t="n">
-        <v>3.489101</v>
+        <v>4.073277</v>
       </c>
     </row>
     <row r="5">
@@ -2545,168 +2545,168 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MobileNet V3</t>
+          <t>MobileNet V2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="C7" t="n">
-        <v>73.7</v>
+        <v>68.7</v>
       </c>
       <c r="D7" t="n">
         <v>67.2</v>
       </c>
       <c r="E7" t="n">
-        <v>15.08907445439999</v>
+        <v>17.10906789958163</v>
       </c>
       <c r="F7" t="n">
-        <v>4.073277</v>
+        <v>3.489099</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MobileNet V2</t>
+          <t>MobileNet V1 (TF_ver_2.0)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="C8" t="n">
-        <v>68.7</v>
+        <v>66.3</v>
       </c>
       <c r="D8" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>17.10906789958163</v>
+        <v>18.45993638441885</v>
       </c>
       <c r="F8" t="n">
-        <v>3.489099</v>
+        <v>4.222061</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MobileNet V1 (TF_ver_2.0)</t>
+          <t>EfficientNet-EdgeTpu (S)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>66.3</v>
+        <v>75.2</v>
       </c>
       <c r="D9" t="n">
         <v>88.09999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>18.45993638441885</v>
+        <v>20.11716436838284</v>
       </c>
       <c r="F9" t="n">
-        <v>4.222061</v>
+        <v>5.413955</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EfficientNet-EdgeTpu (S)</t>
+          <t>Inception V1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="C10" t="n">
-        <v>75.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="D10" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>20.11716436838284</v>
+        <v>33.14868853239102</v>
       </c>
       <c r="F10" t="n">
-        <v>5.413955</v>
+        <v>6.618651</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Inception V1</t>
+          <t>EfficientNet-EdgeTpu (M)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4</v>
+        <v>7.3</v>
       </c>
       <c r="C11" t="n">
-        <v>67.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D11" t="n">
         <v>89.8</v>
       </c>
       <c r="E11" t="n">
-        <v>33.14868853239102</v>
+        <v>54.8856911845842</v>
       </c>
       <c r="F11" t="n">
-        <v>6.618651</v>
+        <v>6.866875</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EfficientNet-EdgeTpu (M)</t>
+          <t>Inception V2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7.3</v>
+        <v>13.4</v>
       </c>
       <c r="C12" t="n">
-        <v>77.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D12" t="n">
         <v>90</v>
       </c>
       <c r="E12" t="n">
-        <v>54.8856911845842</v>
+        <v>213.8192199166669</v>
       </c>
       <c r="F12" t="n">
-        <v>6.866875</v>
+        <v>11.179387</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Inception V2</t>
+          <t>EfficientNet-EdgeTpu (L)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13.4</v>
+        <v>21.3</v>
       </c>
       <c r="C13" t="n">
-        <v>71.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="D13" t="n">
         <v>91.8</v>
       </c>
       <c r="E13" t="n">
-        <v>213.8192199166669</v>
+        <v>226.0427144210526</v>
       </c>
       <c r="F13" t="n">
-        <v>11.179387</v>
+        <v>10.545147</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EfficientNet-EdgeTpu (L)</t>
+          <t>MobileNet V2 (TF_ver_2.0)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21.3</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>79.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D14" t="n">
         <v>93.59999999999999</v>
@@ -2715,7 +2715,7 @@
         <v>226.0427144210526</v>
       </c>
       <c r="F14" t="n">
-        <v>10.545147</v>
+        <v>3.489101</v>
       </c>
     </row>
   </sheetData>
